--- a/ระบบจัดสรรงบประมาณ.xlsx
+++ b/ระบบจัดสรรงบประมาณ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ad82ec08daddac8/Documents/Budget70/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{D99F2231-EAC7-4E41-B28D-DD2EAC30A6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6551A4F1-9B81-466A-B530-A6C975C3475E}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{D99F2231-EAC7-4E41-B28D-DD2EAC30A6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB8A509D-98B2-4C23-80E3-217938A7302F}"/>
   <bookViews>
-    <workbookView xWindow="5985" yWindow="2910" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -3376,6 +3376,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:G177">
   <tableColumns count="7">
